--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135579960</v>
       </c>
       <c r="B2" t="n">
-        <v>92601</v>
+        <v>92628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135579957</v>
       </c>
       <c r="B3" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135579958</v>
       </c>
       <c r="B4" t="n">
-        <v>96081</v>
+        <v>96108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>135579956</v>
       </c>
       <c r="B5" t="n">
-        <v>97352</v>
+        <v>97379</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135639370</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>135639373</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>135639375</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>135579959</v>
       </c>
       <c r="B9" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>135639365</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>135639371</v>
       </c>
       <c r="B11" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>135639369</v>
       </c>
       <c r="B12" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>135639372</v>
       </c>
       <c r="B13" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135744950</v>
       </c>
       <c r="B4" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135753720</v>
       </c>
       <c r="B5" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135579960</v>
       </c>
       <c r="B6" t="n">
-        <v>92633</v>
+        <v>92635</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135744944</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135744947</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135579957</v>
       </c>
       <c r="B9" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>135579958</v>
       </c>
       <c r="B10" t="n">
-        <v>96113</v>
+        <v>96115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135579956</v>
       </c>
       <c r="B11" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135744955</v>
       </c>
       <c r="B12" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135753739</v>
       </c>
       <c r="B13" t="n">
-        <v>97384</v>
+        <v>97386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>135579959</v>
       </c>
       <c r="B40" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>135744933</v>
       </c>
       <c r="B41" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>135753718</v>
       </c>
       <c r="B42" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135753723</v>
       </c>
       <c r="B43" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>135753740</v>
       </c>
       <c r="B44" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>135639365</v>
       </c>
       <c r="B45" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>135753715</v>
       </c>
       <c r="B46" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>135753728</v>
       </c>
       <c r="B47" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135639371</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>135744943</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135744958</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>135753714</v>
       </c>
       <c r="B51" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135753722</v>
       </c>
       <c r="B52" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135753742</v>
       </c>
       <c r="B53" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>135753726</v>
       </c>
       <c r="B54" t="n">
-        <v>103847</v>
+        <v>103849</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135744950</v>
       </c>
       <c r="B4" t="n">
-        <v>92765</v>
+        <v>92779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744957</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135753716</v>
       </c>
       <c r="B3" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744950</v>
       </c>
       <c r="B4" t="n">
-        <v>92779</v>
+        <v>92780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135753720</v>
       </c>
       <c r="B5" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135579960</v>
       </c>
       <c r="B6" t="n">
-        <v>92635</v>
+        <v>92650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135744944</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135744947</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135579957</v>
       </c>
       <c r="B9" t="n">
-        <v>96115</v>
+        <v>96132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>135579958</v>
       </c>
       <c r="B10" t="n">
-        <v>96115</v>
+        <v>96132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135579956</v>
       </c>
       <c r="B11" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135744955</v>
       </c>
       <c r="B12" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135753739</v>
       </c>
       <c r="B13" t="n">
-        <v>97386</v>
+        <v>97403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>135639370</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>135639373</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>135639375</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>135744928</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>135744931</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>135744937</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>135744949</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>135753713</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>135753717</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135753727</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>135753731</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>135753733</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>135753738</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>135753744</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135753748</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135753750</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>135744929</v>
       </c>
       <c r="B30" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>135744932</v>
       </c>
       <c r="B31" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>135744938</v>
       </c>
       <c r="B32" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>135744946</v>
       </c>
       <c r="B33" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>135744926</v>
       </c>
       <c r="B34" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135753719</v>
       </c>
       <c r="B35" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>135744935</v>
       </c>
       <c r="B36" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135753747</v>
       </c>
       <c r="B37" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>135744927</v>
       </c>
       <c r="B38" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>135753725</v>
       </c>
       <c r="B39" t="n">
-        <v>58844</v>
+        <v>58846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>135579959</v>
       </c>
       <c r="B40" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>135744933</v>
       </c>
       <c r="B41" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>135753718</v>
       </c>
       <c r="B42" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135753723</v>
       </c>
       <c r="B43" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>135753740</v>
       </c>
       <c r="B44" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>135639365</v>
       </c>
       <c r="B45" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>135753715</v>
       </c>
       <c r="B46" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>135753728</v>
       </c>
       <c r="B47" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135639371</v>
       </c>
       <c r="B48" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>135744943</v>
       </c>
       <c r="B49" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135744958</v>
       </c>
       <c r="B50" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>135753714</v>
       </c>
       <c r="B51" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135753722</v>
       </c>
       <c r="B52" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135753742</v>
       </c>
       <c r="B53" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>135753726</v>
       </c>
       <c r="B54" t="n">
-        <v>103849</v>
+        <v>103869</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>135639369</v>
       </c>
       <c r="B55" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>135639372</v>
       </c>
       <c r="B56" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>135753734</v>
       </c>
       <c r="B57" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>135753743</v>
       </c>
       <c r="B58" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>135753746</v>
       </c>
       <c r="B59" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744957</v>
       </c>
       <c r="B2" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135753716</v>
       </c>
       <c r="B3" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744950</v>
       </c>
       <c r="B4" t="n">
-        <v>92780</v>
+        <v>92781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135753720</v>
       </c>
       <c r="B5" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135579960</v>
       </c>
       <c r="B6" t="n">
-        <v>92650</v>
+        <v>92651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135744944</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135744947</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135579957</v>
       </c>
       <c r="B9" t="n">
-        <v>96132</v>
+        <v>96133</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>135579958</v>
       </c>
       <c r="B10" t="n">
-        <v>96132</v>
+        <v>96133</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135579956</v>
       </c>
       <c r="B11" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135744955</v>
       </c>
       <c r="B12" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135753739</v>
       </c>
       <c r="B13" t="n">
-        <v>97403</v>
+        <v>97404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>135639370</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>135639373</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>135639375</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>135744928</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>135744931</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>135744937</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>135744949</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>135753713</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>135753717</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135753727</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>135753731</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>135753733</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>135753738</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>135753744</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135753748</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135753750</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>135744929</v>
       </c>
       <c r="B30" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>135744932</v>
       </c>
       <c r="B31" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>135744938</v>
       </c>
       <c r="B32" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>135744946</v>
       </c>
       <c r="B33" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>135579959</v>
       </c>
       <c r="B40" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>135744933</v>
       </c>
       <c r="B41" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>135753718</v>
       </c>
       <c r="B42" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135753723</v>
       </c>
       <c r="B43" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>135753740</v>
       </c>
       <c r="B44" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>135639365</v>
       </c>
       <c r="B45" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>135753715</v>
       </c>
       <c r="B46" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>135753728</v>
       </c>
       <c r="B47" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135639371</v>
       </c>
       <c r="B48" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>135744943</v>
       </c>
       <c r="B49" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135744958</v>
       </c>
       <c r="B50" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>135753714</v>
       </c>
       <c r="B51" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135753722</v>
       </c>
       <c r="B52" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135753742</v>
       </c>
       <c r="B53" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>135753726</v>
       </c>
       <c r="B54" t="n">
-        <v>103869</v>
+        <v>103871</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>135639369</v>
       </c>
       <c r="B55" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>135639372</v>
       </c>
       <c r="B56" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>135753734</v>
       </c>
       <c r="B57" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>135753743</v>
       </c>
       <c r="B58" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>135753746</v>
       </c>
       <c r="B59" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135744950</v>
       </c>
       <c r="B4" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135753720</v>
       </c>
       <c r="B5" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135579960</v>
       </c>
       <c r="B6" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135744944</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135744947</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135579957</v>
       </c>
       <c r="B9" t="n">
-        <v>96133</v>
+        <v>96134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>135579958</v>
       </c>
       <c r="B10" t="n">
-        <v>96133</v>
+        <v>96134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>135579956</v>
       </c>
       <c r="B11" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135744955</v>
       </c>
       <c r="B12" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135753739</v>
       </c>
       <c r="B13" t="n">
-        <v>97404</v>
+        <v>97405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>135579959</v>
       </c>
       <c r="B40" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>135744933</v>
       </c>
       <c r="B41" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>135753718</v>
       </c>
       <c r="B42" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135753723</v>
       </c>
       <c r="B43" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>135753740</v>
       </c>
       <c r="B44" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>135639365</v>
       </c>
       <c r="B45" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>135753715</v>
       </c>
       <c r="B46" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>135753728</v>
       </c>
       <c r="B47" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135639371</v>
       </c>
       <c r="B48" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>135744943</v>
       </c>
       <c r="B49" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135744958</v>
       </c>
       <c r="B50" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>135753714</v>
       </c>
       <c r="B51" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135753722</v>
       </c>
       <c r="B52" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135753742</v>
       </c>
       <c r="B53" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>135753726</v>
       </c>
       <c r="B54" t="n">
-        <v>103871</v>
+        <v>103872</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744957</v>
       </c>
       <c r="B2" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135753716</v>
       </c>
       <c r="B3" t="n">
-        <v>79523</v>
+        <v>79524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135744950</v>
       </c>
       <c r="B4" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>135753720</v>
       </c>
       <c r="B5" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135744944</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135744947</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>135744955</v>
       </c>
       <c r="B12" t="n">
-        <v>97405</v>
+        <v>97406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135753739</v>
       </c>
       <c r="B13" t="n">
-        <v>97405</v>
+        <v>97406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>135639370</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>135639373</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>135639375</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>135744928</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>135744931</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>135744937</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>135744949</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>135753713</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>135753717</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>135753727</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>135753731</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>135753733</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>135753738</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>135753744</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>135753748</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>135753750</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>135744929</v>
       </c>
       <c r="B30" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>135744932</v>
       </c>
       <c r="B31" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         <v>135744938</v>
       </c>
       <c r="B32" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>135744946</v>
       </c>
       <c r="B33" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>135744926</v>
       </c>
       <c r="B34" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>135753719</v>
       </c>
       <c r="B35" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>135744935</v>
       </c>
       <c r="B36" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>135753747</v>
       </c>
       <c r="B37" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>135753725</v>
       </c>
       <c r="B39" t="n">
-        <v>58846</v>
+        <v>58847</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>135744933</v>
       </c>
       <c r="B41" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>135753718</v>
       </c>
       <c r="B42" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>135753723</v>
       </c>
       <c r="B43" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>135753740</v>
       </c>
       <c r="B44" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>135639365</v>
       </c>
       <c r="B45" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>135753715</v>
       </c>
       <c r="B46" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>135753728</v>
       </c>
       <c r="B47" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>135639371</v>
       </c>
       <c r="B48" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>135744943</v>
       </c>
       <c r="B49" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>135744958</v>
       </c>
       <c r="B50" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>135753714</v>
       </c>
       <c r="B51" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>135753722</v>
       </c>
       <c r="B52" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>135753742</v>
       </c>
       <c r="B53" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>135753726</v>
       </c>
       <c r="B54" t="n">
-        <v>103872</v>
+        <v>103873</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>135639369</v>
       </c>
       <c r="B55" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>135639372</v>
       </c>
       <c r="B56" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>135753734</v>
       </c>
       <c r="B57" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>135753743</v>
       </c>
       <c r="B58" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>135753746</v>
       </c>
       <c r="B59" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ59"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135744957</v>
       </c>
       <c r="B2" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135753716</v>
       </c>
       <c r="B3" t="n">
-        <v>79524</v>
+        <v>79528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,45 +904,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135744950</v>
+        <v>135753720</v>
       </c>
       <c r="B4" t="n">
-        <v>92783</v>
+        <v>92069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>721079</v>
+        <v>720832</v>
       </c>
       <c r="R4" t="n">
-        <v>7274258</v>
+        <v>7274296</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,101 +984,84 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744950</t>
+          <t>https://artportalen.se/Sighting/135753720</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135753720</v>
+        <v>135579960</v>
       </c>
       <c r="B5" t="n">
-        <v>92063</v>
+        <v>92652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1179</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Gråträsk, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720832</v>
+        <v>720811</v>
       </c>
       <c r="R5" t="n">
-        <v>7274296</v>
+        <v>7274320</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,22 +1085,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:57</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,69 +1110,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753720</t>
+          <t>https://artportalen.se/Sighting/135579960</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135579960</v>
+        <v>135744944</v>
       </c>
       <c r="B6" t="n">
-        <v>92652</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1179</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gråträsk, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720811</v>
+        <v>720974</v>
       </c>
       <c r="R6" t="n">
-        <v>7274320</v>
+        <v>7274347</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,17 +1192,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,27 +1222,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135579960</t>
+          <t>https://artportalen.se/Sighting/135744944</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135744944</v>
+        <v>135744947</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720974</v>
+        <v>721059</v>
       </c>
       <c r="R7" t="n">
-        <v>7274347</v>
+        <v>7274268</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1309,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1319,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,54 +1345,58 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744944</t>
+          <t>https://artportalen.se/Sighting/135744947</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135744947</v>
+        <v>135579957</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>96134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>2387</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Gråträsk, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>721059</v>
+        <v>721211</v>
       </c>
       <c r="R8" t="n">
-        <v>7274268</v>
+        <v>7274136</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1437,22 +1420,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,24 +1445,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744947</t>
+          <t>https://artportalen.se/Sighting/135579957</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135579957</v>
+        <v>135579958</v>
       </c>
       <c r="B9" t="n">
         <v>96134</v>
@@ -1523,10 +1501,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>721211</v>
+        <v>720930</v>
       </c>
       <c r="R9" t="n">
-        <v>7274136</v>
+        <v>7274331</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1589,16 +1567,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135579957</t>
+          <t>https://artportalen.se/Sighting/135579958</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135579958</v>
+        <v>135579956</v>
       </c>
       <c r="B10" t="n">
-        <v>96134</v>
+        <v>97405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,21 +1584,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2387</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1634,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720930</v>
+        <v>721332</v>
       </c>
       <c r="R10" t="n">
-        <v>7274331</v>
+        <v>7273870</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,16 +1678,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135579958</t>
+          <t>https://artportalen.se/Sighting/135579956</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135579956</v>
+        <v>135744955</v>
       </c>
       <c r="B11" t="n">
-        <v>97405</v>
+        <v>97412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,24 +1712,20 @@
           <t>Girg.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gråträsk, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>721332</v>
+        <v>721227</v>
       </c>
       <c r="R11" t="n">
-        <v>7273870</v>
+        <v>7274162</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,17 +1749,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,27 +1779,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135579956</t>
+          <t>https://artportalen.se/Sighting/135744955</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135744955</v>
+        <v>135753739</v>
       </c>
       <c r="B12" t="n">
-        <v>97406</v>
+        <v>97412</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,17 +1827,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>721227</v>
+        <v>721189</v>
       </c>
       <c r="R12" t="n">
-        <v>7274162</v>
+        <v>7274164</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1887,7 +1866,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1876,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,65 +1891,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744955</t>
+          <t>https://artportalen.se/Sighting/135753739</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135753739</v>
+        <v>135639370</v>
       </c>
       <c r="B13" t="n">
-        <v>97406</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>721189</v>
+        <v>720817</v>
       </c>
       <c r="R13" t="n">
-        <v>7274164</v>
+        <v>7274352</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,22 +1973,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,27 +2003,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753739</t>
+          <t>https://artportalen.se/Sighting/135639370</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135639370</v>
+        <v>135639373</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720817</v>
+        <v>720807</v>
       </c>
       <c r="R14" t="n">
-        <v>7274352</v>
+        <v>7274421</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2111,7 +2090,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2100,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,16 +2126,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135639370</t>
+          <t>https://artportalen.se/Sighting/135639373</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135639373</v>
+        <v>135639375</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,10 +2167,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720807</v>
+        <v>720824</v>
       </c>
       <c r="R15" t="n">
-        <v>7274421</v>
+        <v>7274359</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2223,7 +2202,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2233,7 +2212,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2259,16 +2238,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135639373</t>
+          <t>https://artportalen.se/Sighting/135639375</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135639375</v>
+        <v>135744928</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,13 +2279,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720824</v>
+        <v>720799</v>
       </c>
       <c r="R16" t="n">
-        <v>7274359</v>
+        <v>7274316</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,22 +2309,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,16 +2350,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135639375</t>
+          <t>https://artportalen.se/Sighting/135744928</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135744928</v>
+        <v>135744931</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,13 +2391,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720799</v>
+        <v>720829</v>
       </c>
       <c r="R17" t="n">
-        <v>7274316</v>
+        <v>7274302</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2447,7 +2426,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2436,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,16 +2462,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744928</t>
+          <t>https://artportalen.se/Sighting/135744931</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135744931</v>
+        <v>135744937</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2524,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720829</v>
+        <v>720919</v>
       </c>
       <c r="R18" t="n">
-        <v>7274302</v>
+        <v>7274337</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,7 +2538,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2548,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,16 +2574,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744931</t>
+          <t>https://artportalen.se/Sighting/135744937</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135744937</v>
+        <v>135744949</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2636,10 +2615,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720919</v>
+        <v>721072</v>
       </c>
       <c r="R19" t="n">
-        <v>7274337</v>
+        <v>7274257</v>
       </c>
       <c r="S19" t="n">
         <v>6</v>
@@ -2671,7 +2650,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2660,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2707,16 +2686,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744937</t>
+          <t>https://artportalen.se/Sighting/135744949</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135744949</v>
+        <v>135753713</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2744,17 +2723,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>721072</v>
+        <v>720760</v>
       </c>
       <c r="R20" t="n">
-        <v>7274257</v>
+        <v>7274239</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,7 +2762,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,7 +2772,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,27 +2787,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744949</t>
+          <t>https://artportalen.se/Sighting/135753713</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135753713</v>
+        <v>135753717</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2860,10 +2839,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720760</v>
+        <v>720752</v>
       </c>
       <c r="R21" t="n">
-        <v>7274239</v>
+        <v>7274258</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2895,7 +2874,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,7 +2884,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2931,16 +2910,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753713</t>
+          <t>https://artportalen.se/Sighting/135753717</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135753717</v>
+        <v>135753727</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,10 +2951,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720752</v>
+        <v>720923</v>
       </c>
       <c r="R22" t="n">
-        <v>7274258</v>
+        <v>7274356</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3007,7 +2986,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3017,7 +2996,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3043,16 +3022,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753717</t>
+          <t>https://artportalen.se/Sighting/135753727</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135753727</v>
+        <v>135753731</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3084,13 +3063,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720923</v>
+        <v>721014</v>
       </c>
       <c r="R23" t="n">
-        <v>7274356</v>
+        <v>7274321</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3119,7 +3098,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3129,7 +3108,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3155,16 +3134,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753727</t>
+          <t>https://artportalen.se/Sighting/135753731</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135753731</v>
+        <v>135753733</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3196,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>721014</v>
+        <v>721029</v>
       </c>
       <c r="R24" t="n">
-        <v>7274321</v>
+        <v>7274292</v>
       </c>
       <c r="S24" t="n">
         <v>6</v>
@@ -3231,7 +3210,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3241,7 +3220,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3267,16 +3246,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753731</t>
+          <t>https://artportalen.se/Sighting/135753733</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135753733</v>
+        <v>135753738</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3308,13 +3287,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>721029</v>
+        <v>721129</v>
       </c>
       <c r="R25" t="n">
-        <v>7274292</v>
+        <v>7274237</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3343,7 +3322,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3353,7 +3332,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3379,16 +3358,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753733</t>
+          <t>https://artportalen.se/Sighting/135753738</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135753738</v>
+        <v>135753744</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3420,13 +3399,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>721129</v>
+        <v>721042</v>
       </c>
       <c r="R26" t="n">
-        <v>7274237</v>
+        <v>7274043</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3455,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,7 +3444,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3491,16 +3470,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753738</t>
+          <t>https://artportalen.se/Sighting/135753744</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135753744</v>
+        <v>135753748</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3532,13 +3511,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>721042</v>
+        <v>720880</v>
       </c>
       <c r="R27" t="n">
-        <v>7274043</v>
+        <v>7274154</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3567,7 +3546,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,7 +3556,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3603,16 +3582,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753744</t>
+          <t>https://artportalen.se/Sighting/135753748</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135753748</v>
+        <v>135753750</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,10 +3623,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720880</v>
+        <v>720814</v>
       </c>
       <c r="R28" t="n">
-        <v>7274154</v>
+        <v>7274177</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3679,7 +3658,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3668,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3715,51 +3694,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753748</t>
+          <t>https://artportalen.se/Sighting/135753750</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135753750</v>
+        <v>135744929</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>83436</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720814</v>
+        <v>720803</v>
       </c>
       <c r="R29" t="n">
-        <v>7274177</v>
+        <v>7274314</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3791,7 +3770,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3801,7 +3780,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,27 +3795,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753750</t>
+          <t>https://artportalen.se/Sighting/135744929</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135744929</v>
+        <v>135744932</v>
       </c>
       <c r="B30" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3868,13 +3847,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720803</v>
+        <v>720865</v>
       </c>
       <c r="R30" t="n">
-        <v>7274314</v>
+        <v>7274312</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3903,7 +3882,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3913,7 +3892,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3939,16 +3918,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744929</t>
+          <t>https://artportalen.se/Sighting/135744932</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135744932</v>
+        <v>135744938</v>
       </c>
       <c r="B31" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3980,13 +3959,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720865</v>
+        <v>720929</v>
       </c>
       <c r="R31" t="n">
-        <v>7274312</v>
+        <v>7274373</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4015,7 +3994,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4025,7 +4004,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4051,16 +4030,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744932</t>
+          <t>https://artportalen.se/Sighting/135744938</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135744938</v>
+        <v>135744946</v>
       </c>
       <c r="B32" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4092,13 +4071,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>720929</v>
+        <v>721040</v>
       </c>
       <c r="R32" t="n">
-        <v>7274373</v>
+        <v>7274299</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4127,7 +4106,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4137,7 +4116,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4163,16 +4142,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744938</t>
+          <t>https://artportalen.se/Sighting/135744946</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135744946</v>
+        <v>135744926</v>
       </c>
       <c r="B33" t="n">
-        <v>83432</v>
+        <v>57987</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4180,21 +4159,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4204,10 +4183,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>721040</v>
+        <v>720772</v>
       </c>
       <c r="R33" t="n">
-        <v>7274299</v>
+        <v>7274244</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4239,7 +4218,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4249,7 +4228,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Avbarkad klen gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4275,16 +4259,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744946</t>
+          <t>https://artportalen.se/Sighting/135744926</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135744926</v>
+        <v>135753719</v>
       </c>
       <c r="B34" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4312,17 +4296,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>720772</v>
+        <v>720837</v>
       </c>
       <c r="R34" t="n">
-        <v>7274244</v>
+        <v>7274293</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4351,7 +4335,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4361,12 +4345,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Avbarkad klen gran</t>
+          <t>Födosök, gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4381,27 +4365,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744926</t>
+          <t>https://artportalen.se/Sighting/135753719</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135753719</v>
+        <v>135744935</v>
       </c>
       <c r="B35" t="n">
-        <v>57983</v>
+        <v>58148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4409,37 +4393,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>720837</v>
+        <v>720879</v>
       </c>
       <c r="R35" t="n">
         <v>7274293</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4468,7 +4464,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4478,12 +4474,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Födosök, gran</t>
+          <t>Såg minst 3, kan ha varit fler</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4498,27 +4494,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753719</t>
+          <t>https://artportalen.se/Sighting/135744935</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135744935</v>
+        <v>135753747</v>
       </c>
       <c r="B36" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,30 +4541,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>permanent revir</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>720879</v>
+        <v>720883</v>
       </c>
       <c r="R36" t="n">
-        <v>7274293</v>
+        <v>7274157</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4597,7 +4590,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4607,12 +4600,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Såg minst 3, kan ha varit fler</t>
+          <t>Permanent revir</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4627,74 +4620,65 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744935</t>
+          <t>https://artportalen.se/Sighting/135753747</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135753747</v>
+        <v>135744927</v>
       </c>
       <c r="B37" t="n">
-        <v>58144</v>
+        <v>5202</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>720883</v>
+        <v>720772</v>
       </c>
       <c r="R37" t="n">
-        <v>7274157</v>
+        <v>7274268</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4723,7 +4707,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4733,12 +4717,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Permanent revir</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4753,27 +4732,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753747</t>
+          <t>https://artportalen.se/Sighting/135744927</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135744927</v>
+        <v>135753725</v>
       </c>
       <c r="B38" t="n">
-        <v>5202</v>
+        <v>58851</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4781,34 +4760,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>208249</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>720772</v>
+        <v>720895</v>
       </c>
       <c r="R38" t="n">
-        <v>7274268</v>
+        <v>7274301</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4840,7 +4819,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4829,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4865,27 +4844,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744927</t>
+          <t>https://artportalen.se/Sighting/135753725</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135753725</v>
+        <v>135579959</v>
       </c>
       <c r="B39" t="n">
-        <v>58847</v>
+        <v>99212</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4893,37 +4872,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>208249</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Gråträsk, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>720895</v>
+        <v>720851</v>
       </c>
       <c r="R39" t="n">
-        <v>7274301</v>
+        <v>7274354</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4947,22 +4930,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4977,27 +4955,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753725</t>
+          <t>https://artportalen.se/Sighting/135579959</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135579959</v>
+        <v>135744933</v>
       </c>
       <c r="B40" t="n">
-        <v>99212</v>
+        <v>106428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5005,41 +4983,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gråträsk, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>720851</v>
+        <v>720878</v>
       </c>
       <c r="R40" t="n">
-        <v>7274354</v>
+        <v>7274297</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5063,17 +5037,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5088,27 +5067,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135579959</t>
+          <t>https://artportalen.se/Sighting/135744933</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135744933</v>
+        <v>135753718</v>
       </c>
       <c r="B41" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5136,17 +5115,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>720878</v>
+        <v>720826</v>
       </c>
       <c r="R41" t="n">
-        <v>7274297</v>
+        <v>7274300</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5175,7 +5154,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5185,7 +5164,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5200,27 +5179,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744933</t>
+          <t>https://artportalen.se/Sighting/135753718</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135753718</v>
+        <v>135753723</v>
       </c>
       <c r="B42" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5252,10 +5231,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>720826</v>
+        <v>720862</v>
       </c>
       <c r="R42" t="n">
-        <v>7274300</v>
+        <v>7274311</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5287,7 +5266,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5297,7 +5276,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5323,16 +5302,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753718</t>
+          <t>https://artportalen.se/Sighting/135753723</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135753723</v>
+        <v>135753740</v>
       </c>
       <c r="B43" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5364,13 +5343,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>720862</v>
+        <v>721186</v>
       </c>
       <c r="R43" t="n">
-        <v>7274311</v>
+        <v>7274169</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5399,7 +5378,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5409,7 +5388,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5435,16 +5414,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753723</t>
+          <t>https://artportalen.se/Sighting/135753740</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135753740</v>
+        <v>135639365</v>
       </c>
       <c r="B44" t="n">
-        <v>106422</v>
+        <v>98164</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5452,37 +5431,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>721186</v>
+        <v>720797</v>
       </c>
       <c r="R44" t="n">
-        <v>7274169</v>
+        <v>7274248</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5506,22 +5485,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5536,27 +5515,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753740</t>
+          <t>https://artportalen.se/Sighting/135639365</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135639365</v>
+        <v>135753715</v>
       </c>
       <c r="B45" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5584,14 +5563,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>720797</v>
+        <v>720758</v>
       </c>
       <c r="R45" t="n">
-        <v>7274248</v>
+        <v>7274258</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5618,22 +5597,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5648,27 +5627,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135639365</t>
+          <t>https://artportalen.se/Sighting/135753715</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135753715</v>
+        <v>135753728</v>
       </c>
       <c r="B46" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5700,13 +5679,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>720758</v>
+        <v>720953</v>
       </c>
       <c r="R46" t="n">
-        <v>7274258</v>
+        <v>7274369</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5735,7 +5714,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5745,7 +5724,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5771,16 +5750,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753715</t>
+          <t>https://artportalen.se/Sighting/135753728</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135753728</v>
+        <v>135639371</v>
       </c>
       <c r="B47" t="n">
-        <v>98158</v>
+        <v>99324</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5788,37 +5767,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>720953</v>
+        <v>720781</v>
       </c>
       <c r="R47" t="n">
-        <v>7274369</v>
+        <v>7274378</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5842,22 +5821,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst ett 50tal</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5872,27 +5856,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753728</t>
+          <t>https://artportalen.se/Sighting/135639371</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135639371</v>
+        <v>135744943</v>
       </c>
       <c r="B48" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5924,10 +5908,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>720781</v>
+        <v>720970</v>
       </c>
       <c r="R48" t="n">
-        <v>7274378</v>
+        <v>7274348</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5954,27 +5938,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst ett 50tal</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6000,16 +5979,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135639371</t>
+          <t>https://artportalen.se/Sighting/135744943</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135744943</v>
+        <v>135744958</v>
       </c>
       <c r="B49" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6041,10 +6020,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>720970</v>
+        <v>720912</v>
       </c>
       <c r="R49" t="n">
-        <v>7274348</v>
+        <v>7274125</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6076,7 +6055,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6086,7 +6065,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6112,16 +6091,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744943</t>
+          <t>https://artportalen.se/Sighting/135744958</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135744958</v>
+        <v>135753714</v>
       </c>
       <c r="B50" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6149,14 +6128,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>720912</v>
+        <v>720761</v>
       </c>
       <c r="R50" t="n">
-        <v>7274125</v>
+        <v>7274239</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6188,7 +6167,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6198,7 +6177,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6213,27 +6192,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135744958</t>
+          <t>https://artportalen.se/Sighting/135753714</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135753714</v>
+        <v>135753722</v>
       </c>
       <c r="B51" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6265,10 +6244,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>720761</v>
+        <v>720855</v>
       </c>
       <c r="R51" t="n">
-        <v>7274239</v>
+        <v>7274307</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6300,7 +6279,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6310,7 +6289,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6336,16 +6315,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753714</t>
+          <t>https://artportalen.se/Sighting/135753722</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135753722</v>
+        <v>135753742</v>
       </c>
       <c r="B52" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6377,10 +6356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>720855</v>
+        <v>721196</v>
       </c>
       <c r="R52" t="n">
-        <v>7274307</v>
+        <v>7274158</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6412,7 +6391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6422,7 +6401,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6448,16 +6427,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753722</t>
+          <t>https://artportalen.se/Sighting/135753742</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135753742</v>
+        <v>135753726</v>
       </c>
       <c r="B53" t="n">
-        <v>99318</v>
+        <v>103879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6465,21 +6444,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>222004</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6489,13 +6468,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>721196</v>
+        <v>720922</v>
       </c>
       <c r="R53" t="n">
-        <v>7274158</v>
+        <v>7274344</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6524,7 +6503,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6534,7 +6513,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6560,54 +6539,57 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753742</t>
+          <t>https://artportalen.se/Sighting/135753726</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135753726</v>
+        <v>135639369</v>
       </c>
       <c r="B54" t="n">
-        <v>103873</v>
+        <v>78458</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222004</v>
+        <v>228579</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Flakaberget, Nb</t>
+          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>720922</v>
+        <v>720842</v>
       </c>
       <c r="R54" t="n">
-        <v>7274344</v>
+        <v>7274361</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6631,22 +6613,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6655,33 +6637,34 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753726</t>
+          <t>https://artportalen.se/Sighting/135639369</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135639369</v>
+        <v>135639372</v>
       </c>
       <c r="B55" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6707,22 +6690,19 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flakaberget, Gråträsk V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>720842</v>
+        <v>720818</v>
       </c>
       <c r="R55" t="n">
-        <v>7274361</v>
+        <v>7274389</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6751,7 +6731,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6761,7 +6741,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6770,7 +6750,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6788,16 +6767,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135639369</t>
+          <t>https://artportalen.se/Sighting/135639372</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135639372</v>
+        <v>135753734</v>
       </c>
       <c r="B56" t="n">
-        <v>78454</v>
+        <v>79472</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6805,34 +6784,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Flakaberget, Gråträsk V Piteå, Nb</t>
+          <t>Flakaberget, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>720818</v>
+        <v>721029</v>
       </c>
       <c r="R56" t="n">
-        <v>7274389</v>
+        <v>7274291</v>
       </c>
       <c r="S56" t="n">
         <v>6</v>
@@ -6859,22 +6838,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6889,27 +6868,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135639372</t>
+          <t>https://artportalen.se/Sighting/135753734</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135753734</v>
+        <v>135753743</v>
       </c>
       <c r="B57" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6941,13 +6920,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>721029</v>
+        <v>721230</v>
       </c>
       <c r="R57" t="n">
-        <v>7274291</v>
+        <v>7274098</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6976,7 +6955,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6986,7 +6965,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7012,16 +6991,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135753734</t>
+          <t>https://artportalen.se/Sighting/135753743</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135753743</v>
+        <v>135753746</v>
       </c>
       <c r="B58" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7053,10 +7032,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>721230</v>
+        <v>720950</v>
       </c>
       <c r="R58" t="n">
-        <v>7274098</v>
+        <v>7274104</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7088,7 +7067,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7098,7 +7077,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7123,118 +7102,6 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135753743</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135753746</v>
-      </c>
-      <c r="B59" t="n">
-        <v>79468</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Flakaberget, Nb</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>720950</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7274104</v>
-      </c>
-      <c r="S59" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Piteå socken</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135753746</t>
         </is>
@@ -7299,7 +7166,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744957</v>
       </c>
       <c r="B2" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135753716</v>
       </c>
       <c r="B3" t="n">
-        <v>79528</v>
+        <v>79529</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135753720</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135744944</v>
       </c>
       <c r="B6" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135744947</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>135744955</v>
       </c>
       <c r="B11" t="n">
-        <v>97412</v>
+        <v>97413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>135753739</v>
       </c>
       <c r="B12" t="n">
-        <v>97412</v>
+        <v>97413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135744928</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135744931</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135744937</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>135744949</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>135753713</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135753717</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>135753727</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135753731</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135753733</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135753738</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>135753744</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135753748</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135753750</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>135744929</v>
       </c>
       <c r="B29" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>135744932</v>
       </c>
       <c r="B30" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>135744938</v>
       </c>
       <c r="B31" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135744946</v>
       </c>
       <c r="B32" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>135744926</v>
       </c>
       <c r="B33" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135753719</v>
       </c>
       <c r="B34" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>135744935</v>
       </c>
       <c r="B35" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>135753747</v>
       </c>
       <c r="B36" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>135753725</v>
       </c>
       <c r="B38" t="n">
-        <v>58851</v>
+        <v>58852</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>135744933</v>
       </c>
       <c r="B40" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>135753718</v>
       </c>
       <c r="B41" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135753723</v>
       </c>
       <c r="B42" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135753740</v>
       </c>
       <c r="B43" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>135753715</v>
       </c>
       <c r="B45" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>135753728</v>
       </c>
       <c r="B46" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>135744943</v>
       </c>
       <c r="B48" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>135744958</v>
       </c>
       <c r="B49" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135753714</v>
       </c>
       <c r="B50" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135753722</v>
       </c>
       <c r="B51" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>135753742</v>
       </c>
       <c r="B52" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>135753726</v>
       </c>
       <c r="B53" t="n">
-        <v>103879</v>
+        <v>103880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135753734</v>
       </c>
       <c r="B56" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>135753743</v>
       </c>
       <c r="B57" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>135753746</v>
       </c>
       <c r="B58" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744957</v>
       </c>
       <c r="B2" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135753716</v>
       </c>
       <c r="B3" t="n">
-        <v>79529</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135753720</v>
       </c>
       <c r="B4" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135744944</v>
       </c>
       <c r="B6" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135744947</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>135744955</v>
       </c>
       <c r="B11" t="n">
-        <v>97413</v>
+        <v>97424</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>135753739</v>
       </c>
       <c r="B12" t="n">
-        <v>97413</v>
+        <v>97424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135744928</v>
       </c>
       <c r="B16" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135744931</v>
       </c>
       <c r="B17" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135744937</v>
       </c>
       <c r="B18" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>135744949</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>135753713</v>
       </c>
       <c r="B20" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135753717</v>
       </c>
       <c r="B21" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>135753727</v>
       </c>
       <c r="B22" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135753731</v>
       </c>
       <c r="B23" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135753733</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135753738</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>135753744</v>
       </c>
       <c r="B26" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135753748</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135753750</v>
       </c>
       <c r="B28" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>135744929</v>
       </c>
       <c r="B29" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>135744932</v>
       </c>
       <c r="B30" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>135744938</v>
       </c>
       <c r="B31" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135744946</v>
       </c>
       <c r="B32" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>135744933</v>
       </c>
       <c r="B40" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>135753718</v>
       </c>
       <c r="B41" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135753723</v>
       </c>
       <c r="B42" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135753740</v>
       </c>
       <c r="B43" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>135753715</v>
       </c>
       <c r="B45" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>135753728</v>
       </c>
       <c r="B46" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>135744943</v>
       </c>
       <c r="B48" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>135744958</v>
       </c>
       <c r="B49" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135753714</v>
       </c>
       <c r="B50" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135753722</v>
       </c>
       <c r="B51" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>135753742</v>
       </c>
       <c r="B52" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>135753726</v>
       </c>
       <c r="B53" t="n">
-        <v>103880</v>
+        <v>103891</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135753734</v>
       </c>
       <c r="B56" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>135753743</v>
       </c>
       <c r="B57" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>135753746</v>
       </c>
       <c r="B58" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135744957</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135753716</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135753720</v>
       </c>
       <c r="B4" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135744944</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>135744947</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>135744955</v>
       </c>
       <c r="B11" t="n">
-        <v>97424</v>
+        <v>97437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>135753739</v>
       </c>
       <c r="B12" t="n">
-        <v>97424</v>
+        <v>97437</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135744928</v>
       </c>
       <c r="B16" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135744931</v>
       </c>
       <c r="B17" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135744937</v>
       </c>
       <c r="B18" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>135744949</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>135753713</v>
       </c>
       <c r="B20" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135753717</v>
       </c>
       <c r="B21" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>135753727</v>
       </c>
       <c r="B22" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135753731</v>
       </c>
       <c r="B23" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135753733</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135753738</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>135753744</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135753748</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135753750</v>
       </c>
       <c r="B28" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         <v>135744929</v>
       </c>
       <c r="B29" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>135744932</v>
       </c>
       <c r="B30" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>135744938</v>
       </c>
       <c r="B31" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135744946</v>
       </c>
       <c r="B32" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4151,7 +4151,7 @@
         <v>135744926</v>
       </c>
       <c r="B33" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135753719</v>
       </c>
       <c r="B34" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>135744935</v>
       </c>
       <c r="B35" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>135753747</v>
       </c>
       <c r="B36" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>135753725</v>
       </c>
       <c r="B38" t="n">
-        <v>58852</v>
+        <v>58857</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>135744933</v>
       </c>
       <c r="B40" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>135753718</v>
       </c>
       <c r="B41" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135753723</v>
       </c>
       <c r="B42" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135753740</v>
       </c>
       <c r="B43" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>135753715</v>
       </c>
       <c r="B45" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>135753728</v>
       </c>
       <c r="B46" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>135744943</v>
       </c>
       <c r="B48" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>135744958</v>
       </c>
       <c r="B49" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135753714</v>
       </c>
       <c r="B50" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135753722</v>
       </c>
       <c r="B51" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>135753742</v>
       </c>
       <c r="B52" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>135753726</v>
       </c>
       <c r="B53" t="n">
-        <v>103891</v>
+        <v>103904</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135753734</v>
       </c>
       <c r="B56" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>135753743</v>
       </c>
       <c r="B57" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>135753746</v>
       </c>
       <c r="B58" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>135753720</v>
       </c>
       <c r="B4" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>135753739</v>
       </c>
       <c r="B12" t="n">
-        <v>97437</v>
+        <v>97438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>135753718</v>
       </c>
       <c r="B41" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135753723</v>
       </c>
       <c r="B42" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135753740</v>
       </c>
       <c r="B43" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>135753715</v>
       </c>
       <c r="B45" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>135753728</v>
       </c>
       <c r="B46" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135753714</v>
       </c>
       <c r="B50" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135753722</v>
       </c>
       <c r="B51" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>135753742</v>
       </c>
       <c r="B52" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>135753726</v>
       </c>
       <c r="B53" t="n">
-        <v>103904</v>
+        <v>103905</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 32251-2026 artfynd.xlsx
+++ b/artfynd/A 32251-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135753716</v>
       </c>
       <c r="B3" t="n">
-        <v>79539</v>
+        <v>79552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135753720</v>
       </c>
       <c r="B4" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>135753739</v>
       </c>
       <c r="B12" t="n">
-        <v>97438</v>
+        <v>97451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         <v>135753713</v>
       </c>
       <c r="B20" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>135753717</v>
       </c>
       <c r="B21" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>135753727</v>
       </c>
       <c r="B22" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>135753731</v>
       </c>
       <c r="B23" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>135753733</v>
       </c>
       <c r="B24" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>135753738</v>
       </c>
       <c r="B25" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>135753744</v>
       </c>
       <c r="B26" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>135753748</v>
       </c>
       <c r="B27" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135753750</v>
       </c>
       <c r="B28" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>135753719</v>
       </c>
       <c r="B34" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>135753747</v>
       </c>
       <c r="B36" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>135753725</v>
       </c>
       <c r="B38" t="n">
-        <v>58857</v>
+        <v>58870</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>135753718</v>
       </c>
       <c r="B41" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135753723</v>
       </c>
       <c r="B42" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>135753740</v>
       </c>
       <c r="B43" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>135753715</v>
       </c>
       <c r="B45" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>135753728</v>
       </c>
       <c r="B46" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>135753714</v>
       </c>
       <c r="B50" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>135753722</v>
       </c>
       <c r="B51" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>135753742</v>
       </c>
       <c r="B52" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>135753726</v>
       </c>
       <c r="B53" t="n">
-        <v>103905</v>
+        <v>103918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135753734</v>
       </c>
       <c r="B56" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>135753743</v>
       </c>
       <c r="B57" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>135753746</v>
       </c>
       <c r="B58" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
